--- a/docs/spiderman_1967_episode_clip_guide_updated.xlsx
+++ b/docs/spiderman_1967_episode_clip_guide_updated.xlsx
@@ -2,19 +2,19 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R466d16dcc8064679"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="R6317d9261ba9463a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R4dcf96e04cfb40a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R46ae6df027294db3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="Rb784284c789a4a83"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="R5909aaba183549a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R44dc68dd2a9b4daa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R52b761b74b114e4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R1920378493234696"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="Rd43ef6d48354479f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Rd2da5b8e8ee64a47"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="Rd48fbedc83714c46"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Episode Clip Guide" sheetId="13" r:id="R57f9673479b84507"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R66dc8a6e5f7f4914"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Plan" sheetId="2" r:id="Re113bb0f55af4592"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mini-Wizards" sheetId="3" r:id="R2d3b2f4037374033"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repurposed Modes" sheetId="4" r:id="R3e1570eb228e46eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Rules Snapshot" sheetId="5" r:id="R75844465ec724187"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Progression Case Files" sheetId="6" r:id="Rf3eefbb19dc54c8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Active Todos" sheetId="7" r:id="R4813ca96da5d457f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sources" sheetId="8" r:id="R150ae4b7a9a0462a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chapter Bonuses" sheetId="9" r:id="R27880194865d442d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mode Balance" sheetId="10" r:id="R9dcdb05d758d47a3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Player Var Cleanup" sheetId="11" r:id="Rf22465e05da440f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Status" sheetId="12" r:id="R3613f07dbd0c473e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Episode Clip Guide" sheetId="13" r:id="Rdd4baf7d57a944ee"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -149,34 +149,14 @@
   <x:borders count="10">
     <x:border/>
     <x:border/>
-    <x:border>
-      <x:left/>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:top/>
-    </x:border>
-    <x:border>
-      <x:left/>
-    </x:border>
-    <x:border>
-      <x:right/>
-    </x:border>
-    <x:border>
-      <x:left/>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:bottom/>
-    </x:border>
-    <x:border>
-      <x:right/>
-      <x:bottom/>
-    </x:border>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
+    <x:border/>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -3091,7 +3071,7 @@
         <x:v>Keep</x:v>
       </x:c>
       <x:c r="C2" s="31" t="str">
-        <x:v>harley_clivendon_state, conquistador_state, spider_slayer_state, metal_eating_monster_state, fiddler_state</x:v>
+        <x:v>harley_clivendon_state, conquistador_state, spider_slayer_state, metal_eating_robot_state, fiddler_state</x:v>
       </x:c>
       <x:c r="D2" s="31" t="str">
         <x:v>All five persistent progression states are required.</x:v>
@@ -5507,7 +5487,7 @@
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H4" s="31" t="str">
-        <x:v>Upper playfield/spinner mode; banks vulture_bonus; first 10 music assignment retained.</x:v>
+        <x:v>Upper playfield/spinner mode; banks vulture_bonus; first 10 music assignment ...</x:v>
       </x:c>
       <x:c r="I4" s="31" t="str">
         <x:v>sinister_surge</x:v>
@@ -5539,7 +5519,7 @@
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H5" s="31" t="str">
-        <x:v>Serum at STAR; deliver to web shots. Case files now enhance the loop: Bigger value, slower decay, follow-up jackpots, first expired serum saved, first delivery either web.</x:v>
+        <x:v>Serum at STAR; deliver to web shots. Case files now enhance the loop: Bigger ...</x:v>
       </x:c>
       <x:c r="I5" s="31" t="str">
         <x:v>sinister_surge</x:v>
@@ -5571,7 +5551,7 @@
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H6" s="31" t="str">
-        <x:v>Travelling spark and final Super Jackpot; final-shot/callout delay considered OK.</x:v>
+        <x:v>Travelling spark and final Super Jackpot; final-shot/callout delay considered...</x:v>
       </x:c>
       <x:c r="I6" s="31" t="str">
         <x:v>sinister_surge</x:v>
@@ -5635,7 +5615,7 @@
         <x:v>Implemented / recent rule update</x:v>
       </x:c>
       <x:c r="H8" s="31" t="str">
-        <x:v>Rollovers lock arms; completing left bank locks one arm and enables jackpot; spinner boosts multiplier.</x:v>
+        <x:v>Rollovers lock arms; completing left bank locks one arm and enables jackpot; ...</x:v>
       </x:c>
       <x:c r="I8" s="31" t="str">
         <x:v>mastermind_trap</x:v>
@@ -5667,7 +5647,7 @@
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H9" s="31" t="str">
-        <x:v>Hidden Super/clue mode; wrong shots lower value; first 10 music assignment retained.</x:v>
+        <x:v>Hidden Super/clue mode; wrong shots lower value; first 10 music assignment re...</x:v>
       </x:c>
       <x:c r="I9" s="31" t="str">
         <x:v>mastermind_trap</x:v>
@@ -5763,7 +5743,7 @@
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H12" s="31" t="str">
-        <x:v>Upper targets light saucers; matching saucer scores 2X; timer reset flow needs testing.</x:v>
+        <x:v>Upper targets light saucers; matching saucer scores 2X; timer reset flow need...</x:v>
       </x:c>
       <x:c r="I12" s="31" t="str">
         <x:v>trubble_unleashed</x:v>
@@ -5827,7 +5807,7 @@
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H14" s="31" t="str">
-        <x:v>Three limited-arrow Hunts. Upper entry stages green right-bank targets and red GI; either upper exit prompts the shot, and the first right-bank drop or rubber hit starts a 12s/18s timer.</x:v>
+        <x:v>Three limited-arrow Hunts. Upper entry stages green right-bank targets and re...</x:v>
       </x:c>
       <x:c r="I14" s="31" t="str">
         <x:v>trubble_unleashed</x:v>
@@ -5914,7 +5894,7 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="E17" s="31" t="str">
-        <x:v>master_plan</x:v>
+        <x:v>plotter</x:v>
       </x:c>
       <x:c r="F17" s="31" t="str">
         <x:v>The Plotter</x:v>
@@ -5923,7 +5903,7 @@
         <x:v>Implemented / simplified</x:v>
       </x:c>
       <x:c r="H17" s="31" t="str">
-        <x:v>Pops build information. Two information plus a spinner hit lights one saucer. Collect three scheme jackpots, then shoot the Daily Bugle VUK for the Master Plan Super.</x:v>
+        <x:v>Pops build information. Two information plus a spinner hit lights one saucer....</x:v>
       </x:c>
       <x:c r="I17" s="31" t="str">
         <x:v>crime_wave</x:v>
@@ -5946,16 +5926,16 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="E18" s="31" t="str">
-        <x:v>fly_brothers</x:v>
+        <x:v>fly_twins</x:v>
       </x:c>
       <x:c r="F18" s="31" t="str">
-        <x:v>Fly Brothers</x:v>
+        <x:v>The Fly Twins</x:v>
       </x:c>
       <x:c r="G18" s="31" t="str">
         <x:v>Implemented / recent gate update</x:v>
       </x:c>
       <x:c r="H18" s="31" t="str">
-        <x:v>Gate opens for upper-target access and closes when upper access is no longer needed.</x:v>
+        <x:v>Gate opens for upper-target access and closes when upper access is no longer ...</x:v>
       </x:c>
       <x:c r="I18" s="31" t="str">
         <x:v>crime_wave</x:v>
@@ -5981,7 +5961,7 @@
         <x:v>fifth_avenue_phantom</x:v>
       </x:c>
       <x:c r="F19" s="31" t="str">
-        <x:v>Fifth Avenue Phantom</x:v>
+        <x:v>The Fifth Avenue Phantom</x:v>
       </x:c>
       <x:c r="G19" s="31" t="str">
         <x:v>Implemented / needs playtest polish</x:v>
@@ -6019,7 +5999,7 @@
         <x:v>Implemented / needs light-color polish</x:v>
       </x:c>
       <x:c r="H20" s="31" t="str">
-        <x:v>Cowboy and Ox control three crime zones; zone clears light upper-target jackpots and build the OX Super at center web.</x:v>
+        <x:v>Cowboy and Ox control three crime zones; zone clears light upper-target jackp...</x:v>
       </x:c>
       <x:c r="I20" s="31" t="str">
         <x:v>crime_wave</x:v>
@@ -6051,7 +6031,7 @@
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H21" s="31" t="str">
-        <x:v>Drops build frozen-diamond value; completing the right 5-bank starts a moving saucer shipment chase. STAR freezes the chase and lights all three saucers briefly. Existing diamond_bonus bank is retained.</x:v>
+        <x:v>Drops build frozen-diamond value; completing the right 5-bank starts a moving...</x:v>
       </x:c>
       <x:c r="I21" s="31" t="str">
         <x:v>crime_wave</x:v>
@@ -6083,7 +6063,7 @@
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H22" s="31" t="str">
-        <x:v>The One-Eyed Idol / Fountain of Terror antagonist. Placeholder scoring is active; full design should use hypnosis, the idol, and hidden-scheme reveals.</x:v>
+        <x:v>The One-Eyed Idol / Fountain of Terror antagonist. Placeholder scoring is act...</x:v>
       </x:c>
       <x:c r="I22" s="31" t="str">
         <x:v>the_web_tightens</x:v>
@@ -6115,7 +6095,7 @@
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H23" s="31" t="str">
-        <x:v>Fountain of Terror antagonist. Placeholder scoring is active; full design should use the hidden fort, Fountain of Youth, and pursuit through the ruins.</x:v>
+        <x:v>Fountain of Terror antagonist. Placeholder scoring is active; full design sho...</x:v>
       </x:c>
       <x:c r="I23" s="31" t="str">
         <x:v>the_web_tightens</x:v>
@@ -6147,7 +6127,7 @@
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H24" s="31" t="str">
-        <x:v>Jameson-operated tracking robot. Placeholder scoring is active; full design should feature a moving hunt, capture pressure, and destroying the Slayer.</x:v>
+        <x:v>Jameson-operated tracking robot. Placeholder scoring is active; full design s...</x:v>
       </x:c>
       <x:c r="I24" s="31" t="str">
         <x:v>the_web_tightens</x:v>
@@ -6170,16 +6150,16 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="E25" s="31" t="str">
-        <x:v>metal_eating_monster</x:v>
+        <x:v>metal_eating_robot</x:v>
       </x:c>
       <x:c r="F25" s="31" t="str">
-        <x:v>Metal-Eating Monster</x:v>
+        <x:v>Metal-Eating Robot</x:v>
       </x:c>
       <x:c r="G25" s="31" t="str">
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H25" s="31" t="str">
-        <x:v>Giant robot from Diet of Destruction. Placeholder scoring is active; full design should use consumed playfield areas, magnetic attacks, furnace heat, and the river finish.</x:v>
+        <x:v>Giant robot from Diet of Destruction. Placeholder scoring is active; full des...</x:v>
       </x:c>
       <x:c r="I25" s="31" t="str">
         <x:v>the_web_tightens</x:v>
@@ -6211,7 +6191,7 @@
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H26" s="31" t="str">
-        <x:v>Fiddler on the Loose sound-and-ransom antagonist. Placeholder scoring is active. Persistent fiddler_bonus is wired into end-of-ball bonus and summary display; the full design will define musical sequences and how ransom is banked.</x:v>
+        <x:v>Fiddler on the Loose sound-and-ransom antagonist. Placeholder scoring is acti...</x:v>
       </x:c>
       <x:c r="I26" s="31" t="str">
         <x:v>the_web_tightens</x:v>
@@ -6243,7 +6223,7 @@
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H27" s="31" t="str">
-        <x:v>Hypnosis Reel: spinner reveals true shot among 3 choices; 5 correct shots defeat Pardo; 7 wrong choices lets him escape.</x:v>
+        <x:v>Hypnosis Reel: spinner reveals true shot among 3 choices; 5 correct shots def...</x:v>
       </x:c>
       <x:c r="I27" s="31" t="str">
         <x:v>fifth_dimension_curse</x:v>
@@ -6275,7 +6255,7 @@
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H28" s="31" t="str">
-        <x:v>2-ball Ruby Heist: saucers reveal upper rubies; spinners build value; 3 Ruby JPs light Super; continues until multiball ends.</x:v>
+        <x:v>2-ball Ruby Heist: saucers reveal upper rubies; spinners build value; 3 Ruby ...</x:v>
       </x:c>
       <x:c r="I28" s="31" t="str">
         <x:v>fifth_dimension_curse</x:v>
@@ -6298,16 +6278,16 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="E29" s="31" t="str">
-        <x:v>scarlet_sorcerer</x:v>
+        <x:v>kotep</x:v>
       </x:c>
       <x:c r="F29" s="31" t="str">
-        <x:v>Kotep — The Scarlet Sorcerer</x:v>
+        <x:v>Kotep</x:v>
       </x:c>
       <x:c r="G29" s="31" t="str">
         <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H29" s="31" t="str">
-        <x:v>Four unique demon shots appear one every 4 seconds and never relight. Demon JPs score 200K–350K; after four demons the gate opens for a 20-second 1M VUK Scepter Super. Case files add an optional fifth demon, larger values, 30 seconds, ball save, or timed Shot Assist.</x:v>
+        <x:v>Four unique demon shots appear one every 4 seconds and never relight. Demon J...</x:v>
       </x:c>
       <x:c r="I29" s="31" t="str">
         <x:v>fifth_dimension_curse</x:v>
@@ -6339,7 +6319,7 @@
         <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H30" s="31" t="str">
-        <x:v>Restore six coordinate-based GI regions before the 40-second timer expires. First-time restoration values rise 100K–350K; Bigger starts at 200K, More Time gives 50 seconds, More Jackpots adds a 500K VUK Blackout Jackpot, Safety Net starts ball save, and Shot Assist spots an extra region.</x:v>
+        <x:v>Restore six coordinate-based GI regions before the 40-second timer expires. F...</x:v>
       </x:c>
       <x:c r="I30" s="31" t="str">
         <x:v>fifth_dimension_curse</x:v>
@@ -6371,7 +6351,7 @@
         <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H31" s="31" t="str">
-        <x:v>One green creature area lights at a time from pops, left drops, right drops, webs, and upper targets. Complete three to light all saucers for a 20-second 1M Super. More Jackpots adds a fourth optional area, Bigger raises values, More Time gives 30 seconds, Safety Net adds ball save, and Shot Assist awards the first two areas.</x:v>
+        <x:v>One green creature area lights at a time from pops, left drops, right drops, ...</x:v>
       </x:c>
       <x:c r="I31" s="31" t="str">
         <x:v>fifth_dimension_curse</x:v>
@@ -6435,7 +6415,7 @@
         <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H33" s="31" t="str">
-        <x:v>Rooftop magnetic sweep: upper entrance resets both banks; each upper spin scores 50K and knocks down the next left-to-right target for another 50K. After seven steps only right drop 5 remains for a timed 1M Super. More Jackpots stages left drop 1 for a 500K Magnetic Flux Super.</x:v>
+        <x:v>Rooftop magnetic sweep: upper entrance resets both banks; each upper spin sco...</x:v>
       </x:c>
       <x:c r="I33" s="31" t="str">
         <x:v>mad_science_meltdown</x:v>
@@ -6458,16 +6438,16 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="E34" s="31" t="str">
-        <x:v>professor_pretoris</x:v>
+        <x:v>professor_pretorius</x:v>
       </x:c>
       <x:c r="F34" s="31" t="str">
-        <x:v>Professor Pretoris</x:v>
+        <x:v>Professor Pretorius</x:v>
       </x:c>
       <x:c r="G34" s="31" t="str">
         <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H34" s="31" t="str">
-        <x:v>Reactor Flood: GI starts red in eight horizontal bands. Each web-spinner hit turns the next band blue from bottom to top for 100K. After eight bands, center web lights for a 20-second 1M Super; More Jackpots adds a 10-second left-web Overflow Super.</x:v>
+        <x:v>Reactor Flood: GI starts red in eight horizontal bands. Each web-spinner hit ...</x:v>
       </x:c>
       <x:c r="I34" s="31" t="str">
         <x:v>mad_science_meltdown</x:v>
@@ -6531,7 +6511,7 @@
         <x:v>Implemented / needs playtest</x:v>
       </x:c>
       <x:c r="H36" s="31" t="str">
-        <x:v>Oil Pellet Chase: red GI and one green shot sweep left web, left drops, left pop, center web, right pop, and right drops, reversing every 4 seconds. Five pellets open the gate and light a timed VUK Super; the held-ball finish floods eight GI bands blue before awarding 1M.</x:v>
+        <x:v>Oil Pellet Chase: red GI and one green shot sweep left web, left drops, left ...</x:v>
       </x:c>
       <x:c r="I36" s="31" t="str">
         <x:v>mad_science_meltdown</x:v>
@@ -6563,7 +6543,7 @@
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H37" s="31" t="str">
-        <x:v>Former Radiation Specialist placeholder retained for later redesign. Clive creates the shape-changing tar creature Blotto with the Spirit Scope; Chapter 7 bank is now blotto_bonus.</x:v>
+        <x:v>Former Radiation Specialist placeholder retained for later redesign. Clive cr...</x:v>
       </x:c>
       <x:c r="I37" s="31" t="str">
         <x:v>nature_strikes_back</x:v>
@@ -6586,16 +6566,16 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="E38" s="31" t="str">
-        <x:v>dr_zap</x:v>
+        <x:v>dr_zapp</x:v>
       </x:c>
       <x:c r="F38" s="31" t="str">
-        <x:v>Doctor Zapp</x:v>
+        <x:v>Doctor Zappp</x:v>
       </x:c>
       <x:c r="G38" s="31" t="str">
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H38" s="31" t="str">
-        <x:v>Electrical/weather slot. Full rules still need design around Zapp stealing and activating Irving Caldwell's invention.</x:v>
+        <x:v>Electrical/weather slot. Full rules still need design around Zapp stealing an...</x:v>
       </x:c>
       <x:c r="I38" s="31" t="str">
         <x:v>nature_strikes_back</x:v>
@@ -6618,16 +6598,16 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="E39" s="31" t="str">
-        <x:v>voltan_boomer</x:v>
+        <x:v>bolton_boomer</x:v>
       </x:c>
       <x:c r="F39" s="31" t="str">
-        <x:v>Voltan and Boomer</x:v>
+        <x:v>Bolton and Boomer</x:v>
       </x:c>
       <x:c r="G39" s="31" t="str">
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H39" s="31" t="str">
-        <x:v>Former elemental freeze placeholder retained for later redesign. Thunder Rumble story pair; robberies are hidden inside violent storms and thunderbolt attacks.</x:v>
+        <x:v>Former elemental freeze placeholder retained for later redesign. Thunder Rumb...</x:v>
       </x:c>
       <x:c r="I39" s="31" t="str">
         <x:v>nature_strikes_back</x:v>
@@ -6659,7 +6639,7 @@
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H40" s="31" t="str">
-        <x:v>Snow/weather slot. Living snow creature grows with snowfall and is defeated by draining its electrical charge.</x:v>
+        <x:v>Snow/weather slot. Living snow creature grows with snowfall and is defeated b...</x:v>
       </x:c>
       <x:c r="I40" s="31" t="str">
         <x:v>nature_strikes_back</x:v>
@@ -6691,7 +6671,7 @@
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H41" s="31" t="str">
-        <x:v>Former Ice Monster placeholder retained under the canonical Plutonians identity. Ice-themed encounter should ultimately resolve by helping repair their escape rather than treating them as purely evil.</x:v>
+        <x:v>Former Ice Monster placeholder retained under the canonical Plutonians identi...</x:v>
       </x:c>
       <x:c r="I41" s="31" t="str">
         <x:v>nature_strikes_back</x:v>
@@ -6723,7 +6703,7 @@
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H42" s="31" t="str">
-        <x:v>Phantom from the Depths of Time villain. Dr. Manta rules the hidden city and uses robotic creatures to freeze and enslave its people.</x:v>
+        <x:v>Phantom from the Depths of Time villain. Dr. Manta rules the hidden city and ...</x:v>
       </x:c>
       <x:c r="I42" s="31" t="str">
         <x:v>invasion_from_everywhere</x:v>
@@ -6755,7 +6735,7 @@
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H43" s="31" t="str">
-        <x:v>Dr. Manta's assistant from the same episode. Moved from Chapter 9 and corrected from Eigor.</x:v>
+        <x:v>Dr. Manta's assistant from the same episode. Moved from Chapter 9 and correct...</x:v>
       </x:c>
       <x:c r="I43" s="31" t="str">
         <x:v>invasion_from_everywhere</x:v>
@@ -6787,7 +6767,7 @@
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H44" s="31" t="str">
-        <x:v>Atlantean invasion from Up from Nowhere; attempts to dome Manhattan and sink it beneath the sea.</x:v>
+        <x:v>Atlantean invasion from Up from Nowhere; attempts to dome Manhattan and sink ...</x:v>
       </x:c>
       <x:c r="I44" s="31" t="str">
         <x:v>invasion_from_everywhere</x:v>
@@ -6819,7 +6799,7 @@
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H45" s="31" t="str">
-        <x:v>Ruler of the hidden Cloud City of Gold. Former Chapter 8 open placeholder retained for later episode-based design.</x:v>
+        <x:v>Ruler of the hidden Cloud City of Gold. Former Chapter 8 open placeholder ret...</x:v>
       </x:c>
       <x:c r="I45" s="31" t="str">
         <x:v>invasion_from_everywhere</x:v>
@@ -6845,13 +6825,13 @@
         <x:v>molemen</x:v>
       </x:c>
       <x:c r="F46" s="31" t="str">
-        <x:v>Molemen</x:v>
+        <x:v>The Molemen</x:v>
       </x:c>
       <x:c r="G46" s="31" t="str">
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H46" s="31" t="str">
-        <x:v>Underground-world mode associated with Mugs Reilly and the Molemen. Compact live name remains Molemen.</x:v>
+        <x:v>Underground-world mode associated with Mugs Reilly and the Molemen. Compact l...</x:v>
       </x:c>
       <x:c r="I46" s="31" t="str">
         <x:v>invasion_from_everywhere</x:v>
@@ -6947,7 +6927,7 @@
         <x:v>Implemented repurpose / needs playtest</x:v>
       </x:c>
       <x:c r="H49" s="31" t="str">
-        <x:v>Former Kingpin limited-shot pursuit repurposed for Desperado. Complete all five unique right-bank targets in escalating rounds before the timer expires; left-bank completion adds time. More Jackpots adds a final showdown jackpot.</x:v>
+        <x:v>Former Kingpin limited-shot pursuit repurposed for Desperado. Complete all fi...</x:v>
       </x:c>
       <x:c r="I49" s="31" t="str">
         <x:v>who_is_the_real_villain</x:v>
@@ -6979,7 +6959,7 @@
         <x:v>Implemented / needs playtest polish</x:v>
       </x:c>
       <x:c r="H50" s="31" t="str">
-        <x:v>Former The Fly Rooftop Swarm rules rethemed as a limited-flip assault on Skymaster's blimp. Saucers open access; three upper targets score Jackpots and a remaining-flips Super.</x:v>
+        <x:v>Former The Fly Rooftop Swarm rules rethemed as a limited-flip assault on Skym...</x:v>
       </x:c>
       <x:c r="I50" s="31" t="str">
         <x:v>who_is_the_real_villain</x:v>
@@ -7002,10 +6982,10 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="E51" s="31" t="str">
-        <x:v>swamp_reptiles</x:v>
+        <x:v>conners_reptiles</x:v>
       </x:c>
       <x:c r="F51" s="31" t="str">
-        <x:v>Swamp Reptiles</x:v>
+        <x:v>Conner's Reptiles</x:v>
       </x:c>
       <x:c r="G51" s="31" t="str">
         <x:v>Implemented repurpose / needs polish</x:v>
@@ -7043,7 +7023,7 @@
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H52" s="31" t="str">
-        <x:v>Knight Must Fall medieval time-displacement slot. Placeholder rules retained until the full Sir Galahad mode is designed.</x:v>
+        <x:v>Knight Must Fall medieval time-displacement slot. Placeholder rules retained ...</x:v>
       </x:c>
       <x:c r="I52" s="31" t="str">
         <x:v>time_tossed_showdown</x:v>
@@ -7075,7 +7055,7 @@
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H53" s="31" t="str">
-        <x:v>Prehistoric Forbidden City and spreading-vine story from Vine. Full episode-based design still needed.</x:v>
+        <x:v>Prehistoric Forbidden City and spreading-vine story from Vine. Full episode-b...</x:v>
       </x:c>
       <x:c r="I53" s="31" t="str">
         <x:v>time_tossed_showdown</x:v>
@@ -7107,7 +7087,7 @@
         <x:v>Implemented repurpose / needs polish</x:v>
       </x:c>
       <x:c r="H54" s="31" t="str">
-        <x:v>Working drop-built spinner-value mode retained. Theme draws from Swing City and Manhattan being lifted into the sky.</x:v>
+        <x:v>Working drop-built spinner-value mode retained. Theme draws from Swing City a...</x:v>
       </x:c>
       <x:c r="I54" s="31" t="str">
         <x:v>time_tossed_showdown</x:v>
@@ -7139,7 +7119,7 @@
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H55" s="31" t="str">
-        <x:v>Alien Spider-Men from Home. Placeholder rules retained; final design should focus on identifying the real Spider-Man and resolving the encounter.</x:v>
+        <x:v>Alien Spider-Men from Home. Placeholder rules retained; final design should f...</x:v>
       </x:c>
       <x:c r="I55" s="31" t="str">
         <x:v>time_tossed_showdown</x:v>
@@ -7171,7 +7151,7 @@
         <x:v>Placeholder/simple active mode</x:v>
       </x:c>
       <x:c r="H56" s="31" t="str">
-        <x:v>Sky Harbor's World War I aerial invasion and paralysis technology. Placeholder rules retained until full design.</x:v>
+        <x:v>Sky Harbor's World War I aerial invasion and paralysis technology. Placeholde...</x:v>
       </x:c>
       <x:c r="I56" s="31" t="str">
         <x:v>time_tossed_showdown</x:v>
@@ -7318,7 +7298,7 @@
         <x:v>Every Jackpot and Super Jackpot adds 20K × the chapter's collected Case Files (0–25 files, for a 0–500K bonus). Ordinary switch, spinner, target, progress, and other non-jackpot scoring do not receive this bonus.</x:v>
       </x:c>
       <x:c r="G5" s="31" t="str">
-        <x:v>Implemented 3-ball multiball. Five timed villain areas: Plotter/pops, Fly Brothers/upper targets, Fifth Avenue Phantom/right bank, Enforcers/left bank, Doctor Cool/saucers. Gate opens at 3+ lit areas and closes at 1 or 0. Upper exits collect jackpots based on currently lit areas. Saucers hold for 15 seconds.</x:v>
+        <x:v>Implemented 3-ball multiball. Five timed villain areas: Plotter/pops, The Fly Twins/upper targets, Fifth Avenue Phantom/right bank, Enforcers/left bank, Doctor Cool/saucers. Gate opens at 3+ lit areas and closes at 1 or 0. Upper exits collect jackpots based on currently lit areas. Saucers hold for 15 seconds.</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -7539,13 +7519,13 @@
         <x:v>reptilla</x:v>
       </x:c>
       <x:c r="B2" s="31" t="str">
-        <x:v>swamp_reptiles</x:v>
+        <x:v>conners_reptiles</x:v>
       </x:c>
       <x:c r="C2" s="31" t="str">
-        <x:v>Swamp Reptiles</x:v>
+        <x:v>Conner's Reptiles</x:v>
       </x:c>
       <x:c r="D2" s="31" t="str">
-        <x:v>Reptilla code repurposed; active key is swamp_reptiles.</x:v>
+        <x:v>Reptilla code repurposed; active key is conners_reptiles.</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -7581,10 +7561,10 @@
         <x:v>frederick_foswell</x:v>
       </x:c>
       <x:c r="B5" s="31" t="str">
-        <x:v>master_plan</x:v>
+        <x:v>plotter</x:v>
       </x:c>
       <x:c r="C5" s="31" t="str">
-        <x:v>Plotter's Master Plan</x:v>
+        <x:v>Plotter's The Plotter</x:v>
       </x:c>
       <x:c r="D5" s="31" t="str">
         <x:v>Foswell rumor/headline economy repurposed as Chapter 4 wizard.</x:v>
@@ -7637,13 +7617,13 @@
         <x:v>fly_twins</x:v>
       </x:c>
       <x:c r="B9" s="31" t="str">
-        <x:v>fly_brothers</x:v>
+        <x:v>fly_twins</x:v>
       </x:c>
       <x:c r="C9" s="31" t="str">
-        <x:v>Fly Brothers</x:v>
+        <x:v>The Fly Twins</x:v>
       </x:c>
       <x:c r="D9" s="31" t="str">
-        <x:v>Human Flies renamed to Fly Brothers; internal mode key, events, player variables, display text, and widget standardized.</x:v>
+        <x:v>Human Flies renamed to The Fly Twins; internal mode key, events, player variables, display text, and widget standardized.</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -7693,10 +7673,10 @@
         <x:v>elemental_freeze_placeholder</x:v>
       </x:c>
       <x:c r="B13" s="31" t="str">
-        <x:v>voltan_boomer</x:v>
+        <x:v>bolton_boomer</x:v>
       </x:c>
       <x:c r="C13" s="31" t="str">
-        <x:v>Voltan and Boomer</x:v>
+        <x:v>Bolton and Boomer</x:v>
       </x:c>
       <x:c r="D13" s="31" t="str">
         <x:v>Neutral Elemental placeholder assigned to the Thunder Rumble story pair.</x:v>
@@ -7752,7 +7732,7 @@
         <x:v>molemen</x:v>
       </x:c>
       <x:c r="C17" s="31" t="str">
-        <x:v>Molemen</x:v>
+        <x:v>The Molemen</x:v>
       </x:c>
       <x:c r="D17" s="31" t="str">
         <x:v>Unverified Antarcticans identity replaced by Molemen; placeholder gameplay retained.</x:v>
@@ -7794,7 +7774,7 @@
         <x:v>molemen</x:v>
       </x:c>
       <x:c r="C20" s="31" t="str">
-        <x:v>Molemen</x:v>
+        <x:v>The Molemen</x:v>
       </x:c>
       <x:c r="D20" s="31" t="str">
         <x:v>Compact widget and mode name; Mugs Reilly can appear on selection, intro, and summary screens.</x:v>
@@ -7889,10 +7869,10 @@
         <x:v>new_chapter_slot</x:v>
       </x:c>
       <x:c r="B27" s="14" t="str">
-        <x:v>metal_eating_monster</x:v>
+        <x:v>metal_eating_robot</x:v>
       </x:c>
       <x:c r="C27" s="14" t="str">
-        <x:v>Metal-Eating Monster</x:v>
+        <x:v>Metal-Eating Robot</x:v>
       </x:c>
       <x:c r="D27" s="14" t="str">
         <x:v>New Chapter 5 placeholder mode created for Danger Lurks.</x:v>
@@ -7917,18 +7897,18 @@
         <x:v>kingpin_regular_slot</x:v>
       </x:c>
       <x:c r="B29" s="14" t="str">
-        <x:v>master_plan</x:v>
+        <x:v>plotter</x:v>
       </x:c>
       <x:c r="C29" s="14" t="str">
         <x:v>The Plotter</x:v>
       </x:c>
       <x:c r="D29" s="14" t="str">
-        <x:v>Kingpin leaves the Chapter 4 villain roster. The former Plotter's Master Plan wizard is simplified into The Plotter regular villain mode.</x:v>
+        <x:v>Kingpin leaves the Chapter 4 villain roster. The former Plotter's The Plotter wizard is simplified into The Plotter regular villain mode.</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="14" t="str">
-        <x:v>master_plan_wizard</x:v>
+        <x:v>plotter_wizard</x:v>
       </x:c>
       <x:c r="B30" s="14" t="str">
         <x:v>crime_wave</x:v>
@@ -9770,7 +9750,7 @@
         <x:v>Playtest first 4 wizards</x:v>
       </x:c>
       <x:c r="C2" s="45" t="str">
-        <x:v>Sinister Surge, Mastermind Trap, Trubble Unleashed, Master Plan.</x:v>
+        <x:v>Sinister Surge, Mastermind Trap, Trubble Unleashed, The Plotter.</x:v>
       </x:c>
       <x:c r="D2" s="45" t="str">
         <x:v>Open</x:v>
@@ -9868,7 +9848,7 @@
         <x:v>Light color cleanup</x:v>
       </x:c>
       <x:c r="C9" s="45" t="str">
-        <x:v>Centaur, Diana, Enforcers, Swamp Reptiles; especially tinted right 5-bank/GI colors.</x:v>
+        <x:v>Centaur, Diana, Enforcers, Conner's Reptiles; especially tinted right 5-bank/GI colors.</x:v>
       </x:c>
       <x:c r="D9" s="45" t="str">
         <x:v>Open</x:v>
@@ -9994,7 +9974,7 @@
         <x:v>Villain music transition-track cleanup</x:v>
       </x:c>
       <x:c r="C18" s="14" t="str">
-        <x:v>Reassigned Trubble Unleashed to motorcycle_circus; Fifth Avenue Phantom to waiting; Master Plan to fbi; The Plutonians to the_shadows; Nature Strikes Back to don_and_dewey. Selection/intro/summary tracks remain unchanged.</x:v>
+        <x:v>Reassigned Trubble Unleashed to motorcycle_circus; Fifth Avenue Phantom to waiting; The Plotter to fbi; The Plutonians to the_shadows; Nature Strikes Back to don_and_dewey. Selection/intro/summary tracks remain unchanged.</x:v>
       </x:c>
       <x:c r="D18" s="14" t="str">
         <x:v>Implemented - needs test</x:v>
@@ -10391,10 +10371,10 @@
         <x:v>Savage Oddities</x:v>
       </x:c>
       <x:c r="C11" s="31" t="str">
-        <x:v>Swamp Reptiles</x:v>
+        <x:v>Conner's Reptiles</x:v>
       </x:c>
       <x:c r="D11" s="31" t="str">
-        <x:v>swamp_reptiles</x:v>
+        <x:v>conners_reptiles</x:v>
       </x:c>
       <x:c r="E11" s="31" t="str">
         <x:v>swamp_bonus</x:v>
